--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127107782</v>
+        <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525444</v>
+        <v>525471</v>
       </c>
       <c r="R3" t="n">
-        <v>7000072</v>
+        <v>7000089</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,11 +879,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +907,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127107451</v>
+        <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,13 +983,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525471</v>
+        <v>525444</v>
       </c>
       <c r="R4" t="n">
-        <v>7000089</v>
+        <v>7000072</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,26 +1016,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1004,31 +1029,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,42 +1734,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R10" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,11 +1794,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1833,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B11" t="n">
-        <v>91241</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,34 +1831,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R11" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,6 +1899,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98335</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172823</v>
+        <v>127172824</v>
       </c>
       <c r="B19" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525403</v>
+        <v>525477</v>
       </c>
       <c r="R19" t="n">
-        <v>7000174</v>
+        <v>7000122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172824</v>
+        <v>127172823</v>
       </c>
       <c r="B20" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525477</v>
+        <v>525403</v>
       </c>
       <c r="R20" t="n">
-        <v>7000122</v>
+        <v>7000174</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -2660,7 +2660,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172824</v>
+        <v>127172823</v>
       </c>
       <c r="B19" t="n">
         <v>91321</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525477</v>
+        <v>525403</v>
       </c>
       <c r="R19" t="n">
-        <v>7000122</v>
+        <v>7000174</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172823</v>
+        <v>127172824</v>
       </c>
       <c r="B20" t="n">
         <v>91321</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525403</v>
+        <v>525477</v>
       </c>
       <c r="R20" t="n">
-        <v>7000174</v>
+        <v>7000122</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172823</v>
+        <v>127172824</v>
       </c>
       <c r="B19" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525403</v>
+        <v>525477</v>
       </c>
       <c r="R19" t="n">
-        <v>7000174</v>
+        <v>7000122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172824</v>
+        <v>127172823</v>
       </c>
       <c r="B20" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525477</v>
+        <v>525403</v>
       </c>
       <c r="R20" t="n">
-        <v>7000122</v>
+        <v>7000174</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -2660,7 +2660,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172824</v>
+        <v>127172823</v>
       </c>
       <c r="B19" t="n">
         <v>91322</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525477</v>
+        <v>525403</v>
       </c>
       <c r="R19" t="n">
-        <v>7000122</v>
+        <v>7000174</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172823</v>
+        <v>127172824</v>
       </c>
       <c r="B20" t="n">
         <v>91322</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525403</v>
+        <v>525477</v>
       </c>
       <c r="R20" t="n">
-        <v>7000174</v>
+        <v>7000122</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98342</v>
+        <v>98346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127107359</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127107258</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127108009</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>127172817</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>127172818</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127172821</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127172820</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -2660,7 +2660,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172823</v>
+        <v>127172824</v>
       </c>
       <c r="B19" t="n">
         <v>91326</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525403</v>
+        <v>525477</v>
       </c>
       <c r="R19" t="n">
-        <v>7000174</v>
+        <v>7000122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172824</v>
+        <v>127172823</v>
       </c>
       <c r="B20" t="n">
         <v>91326</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525477</v>
+        <v>525403</v>
       </c>
       <c r="R20" t="n">
-        <v>7000122</v>
+        <v>7000174</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -2660,7 +2660,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172824</v>
+        <v>127172823</v>
       </c>
       <c r="B19" t="n">
         <v>91326</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525477</v>
+        <v>525403</v>
       </c>
       <c r="R19" t="n">
-        <v>7000122</v>
+        <v>7000174</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172823</v>
+        <v>127172824</v>
       </c>
       <c r="B20" t="n">
         <v>91326</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525403</v>
+        <v>525477</v>
       </c>
       <c r="R20" t="n">
-        <v>7000174</v>
+        <v>7000122</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127107451</v>
+        <v>127107782</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525471</v>
+        <v>525444</v>
       </c>
       <c r="R3" t="n">
-        <v>7000089</v>
+        <v>7000072</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,26 +879,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,31 +892,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -948,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127107782</v>
+        <v>127107451</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525444</v>
+        <v>525471</v>
       </c>
       <c r="R4" t="n">
-        <v>7000072</v>
+        <v>7000089</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,11 +976,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1029,6 +1004,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127107359</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127107258</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127108009</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,34 +1734,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R10" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,6 +1802,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>91328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,42 +1844,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R11" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,11 +1904,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,7 +1933,7 @@
         <v>127172818</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127172821</v>
       </c>
       <c r="B17" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127172820</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127107782</v>
+        <v>127107451</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525444</v>
+        <v>525471</v>
       </c>
       <c r="R3" t="n">
-        <v>7000072</v>
+        <v>7000089</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,11 +879,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +907,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,7 +948,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127107451</v>
+        <v>127107782</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -943,13 +983,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525471</v>
+        <v>525444</v>
       </c>
       <c r="R4" t="n">
-        <v>7000089</v>
+        <v>7000072</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,26 +1016,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1004,31 +1029,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,42 +1734,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R10" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,11 +1794,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1833,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B11" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,34 +1831,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R11" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,6 +1899,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127107359</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127107258</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127108009</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B10" t="n">
-        <v>91334</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,34 +1734,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R10" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,6 +1802,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,42 +1844,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R11" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,11 +1904,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,7 +1933,7 @@
         <v>127172818</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127172821</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127172820</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98358</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127107359</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127107258</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127108009</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,42 +1734,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R10" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,11 +1794,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1833,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B11" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,34 +1831,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R11" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,6 +1899,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,7 +1933,7 @@
         <v>127172818</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127172821</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127172820</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,34 +1734,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R10" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,6 +1802,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,42 +1844,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R11" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,11 +1904,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98490</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127107359</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98488</v>
+        <v>98457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127107258</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127108009</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>91315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,42 +1734,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R10" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,11 +1794,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1833,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B11" t="n">
-        <v>91346</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,34 +1831,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R11" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,6 +1899,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,7 +1933,7 @@
         <v>127172818</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127172821</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127172820</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91346</v>
+        <v>91315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91346</v>
+        <v>91315</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127107646</v>
       </c>
       <c r="B2" t="n">
-        <v>98335</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>127107451</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>127107782</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>127107496</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>127107359</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>127107945</v>
       </c>
       <c r="B7" t="n">
-        <v>98457</v>
+        <v>98488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127107258</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127108009</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172825</v>
+        <v>127172817</v>
       </c>
       <c r="B10" t="n">
-        <v>91315</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,34 +1734,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525486</v>
+        <v>525277</v>
       </c>
       <c r="R10" t="n">
-        <v>7000115</v>
+        <v>7000243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,6 +1802,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172817</v>
+        <v>127172825</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>91346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,42 +1844,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525277</v>
+        <v>525486</v>
       </c>
       <c r="R11" t="n">
-        <v>7000243</v>
+        <v>7000115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,11 +1904,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,7 +1933,7 @@
         <v>127172818</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127172827</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127172822</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>127172826</v>
       </c>
       <c r="B16" t="n">
-        <v>91337</v>
+        <v>91368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127172821</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127172820</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127172823</v>
       </c>
       <c r="B19" t="n">
-        <v>91315</v>
+        <v>91346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>127172824</v>
       </c>
       <c r="B20" t="n">
-        <v>91315</v>
+        <v>91346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127107646</v>
+        <v>127172823</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219795</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525460</v>
+        <v>525403</v>
       </c>
       <c r="R2" t="n">
-        <v>7000088</v>
+        <v>7000174</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,26 +743,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 2 plantor i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -790,31 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127107451</v>
+        <v>127172824</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525471</v>
+        <v>525477</v>
       </c>
       <c r="R3" t="n">
-        <v>7000089</v>
+        <v>7000122</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,26 +840,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,51 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127107782</v>
+        <v>127172825</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525444</v>
+        <v>525486</v>
       </c>
       <c r="R4" t="n">
-        <v>7000072</v>
+        <v>7000115</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,79 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127107496</v>
+        <v>127107451</v>
       </c>
       <c r="B5" t="n">
-        <v>98490</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525465</v>
+        <v>525471</v>
       </c>
       <c r="R5" t="n">
-        <v>7000080</v>
+        <v>7000089</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1036,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1046,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 3 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,6 +1066,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1181,58 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127107359</v>
+        <v>127107782</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525459</v>
+        <v>525444</v>
       </c>
       <c r="R6" t="n">
-        <v>7000099</v>
+        <v>7000072</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,26 +1171,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1287,21 +1184,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1318,62 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127107945</v>
+        <v>127172827</v>
       </c>
       <c r="B7" t="n">
-        <v>98488</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525466</v>
+        <v>525474</v>
       </c>
       <c r="R7" t="n">
-        <v>7000083</v>
+        <v>7000087</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1413,31 +1281,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127107258</v>
+        <v>127172822</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,47 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525518</v>
+        <v>525269</v>
       </c>
       <c r="R8" t="n">
-        <v>7000101</v>
+        <v>7000209</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,26 +1365,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en grov gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1540,68 +1378,43 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127108009</v>
+        <v>127107359</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1615,16 +1428,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Digerberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525535</v>
+        <v>525459</v>
       </c>
       <c r="R9" t="n">
-        <v>7000114</v>
+        <v>7000099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1656,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1666,12 +1484,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,24 +1506,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1723,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172817</v>
+        <v>127107258</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,27 +1560,29 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Digerberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525277</v>
+        <v>525518</v>
       </c>
       <c r="R10" t="n">
-        <v>7000243</v>
+        <v>7000101</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1799,14 +1609,24 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska, på en grov gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,26 +1637,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127172825</v>
+        <v>127108009</v>
       </c>
       <c r="B11" t="n">
-        <v>91346</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,34 +1689,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525486</v>
+        <v>525535</v>
       </c>
       <c r="R11" t="n">
-        <v>7000115</v>
+        <v>7000114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1901,11 +1751,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1914,26 +1779,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172818</v>
+        <v>127172817</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525362</v>
+        <v>525277</v>
       </c>
       <c r="R12" t="n">
-        <v>7000191</v>
+        <v>7000243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2040,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172827</v>
+        <v>127172818</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,34 +1941,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525474</v>
+        <v>525362</v>
       </c>
       <c r="R13" t="n">
-        <v>7000087</v>
+        <v>7000191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2111,6 +2009,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,7 +2043,7 @@
         <v>127172819</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172822</v>
+        <v>127172820</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,34 +2161,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525269</v>
+        <v>525443</v>
       </c>
       <c r="R15" t="n">
-        <v>7000209</v>
+        <v>7000118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,6 +2229,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172826</v>
+        <v>127172821</v>
       </c>
       <c r="B16" t="n">
-        <v>91368</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,34 +2271,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525301</v>
+        <v>525306</v>
       </c>
       <c r="R16" t="n">
-        <v>7000237</v>
+        <v>7000199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2441,60 +2369,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127172821</v>
+        <v>127107646</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>99017</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>219795</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Digerberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525306</v>
+        <v>525460</v>
       </c>
       <c r="R17" t="n">
-        <v>7000199</v>
+        <v>7000088</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2521,11 +2456,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 2 plantor i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2534,69 +2484,85 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127172820</v>
+        <v>127107496</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>99142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Digerberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525443</v>
+        <v>525465</v>
       </c>
       <c r="R18" t="n">
-        <v>7000118</v>
+        <v>7000080</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,14 +2592,24 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 7 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,64 +2620,83 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172823</v>
+        <v>127107945</v>
       </c>
       <c r="B19" t="n">
-        <v>91346</v>
+        <v>99140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Digerberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525403</v>
+        <v>525466</v>
       </c>
       <c r="R19" t="n">
-        <v>7000174</v>
+        <v>7000083</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2741,116 +2736,24 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>127172824</v>
-      </c>
-      <c r="B20" t="n">
-        <v>91346</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Digerberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>525477</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7000122</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Stugun</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4591-2024 artfynd.xlsx
+++ b/artfynd/A 4591-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172823</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107451</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107782</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172827</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107258</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1817,6 +1867,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127108009</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172817</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2037,6 +2097,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172818</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172819</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2257,6 +2327,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172820</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2366,6 +2441,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172821</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107646</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2638,6 +2723,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107496</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2754,8 +2844,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127107945</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>